--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AADC04ED-522D-4C77-A49C-B4B0788BE721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{99BA612D-6185-49A1-8D4B-39A1E8D4BC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -621,13 +621,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH05,S04aH03,S01aH03,S03aH02,S02aH02,S01aH02,S04aH04,S03aH04,S04aH02,S01aH05,S04aH05,S02aH03,S03aH03,S01aH04,S02aH04,S02aH05</t>
+    <t>S04aH03,S01aH04,S02aH03,S03aH02,S03aH05,S04aH02,S01aH02,S04aH04,S03aH04,S03aH03,S01aH03,S02aH02,S04aH05,S01aH05,S02aH04,S02aH05</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH01,S03aH01,S01aH06,S03aH06,S01aH01,S04aH01,S04aH06,S02aH06</t>
+    <t>S02aH01,S01aH01,S04aH01,S04aH06,S03aH06,S03aH01,S01aH06,S02aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH01,S03aH01,S01aH06,S03aH06,S01aH01,S04aH01,S04aH06,S02aH06</v>
+        <v>S02aH01,S01aH01,S04aH01,S04aH06,S03aH06,S03aH01,S01aH06,S02aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH05,S04aH03,S01aH03,S03aH02,S02aH02,S01aH02,S04aH04,S03aH04,S04aH02,S01aH05,S04aH05,S02aH03,S03aH03,S01aH04,S02aH04,S02aH05</v>
+        <v>S04aH03,S01aH04,S02aH03,S03aH02,S03aH05,S04aH02,S01aH02,S04aH04,S03aH04,S03aH03,S01aH03,S02aH02,S04aH05,S01aH05,S02aH04,S02aH05</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1350,7 +1350,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{417A718C-95BC-4500-BD39-27D70185CFFA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4612908-28BC-4D55-B9B8-A1E4D1F94813}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1456,7 +1456,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{437197F4-87ED-43DC-A078-093BFEC136C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE41091-0AD1-4372-9867-C36866FE65A8}">
   <dimension ref="B9:O490"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16878,7 +16878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25D56D9E-AEBD-40EB-A271-F311490FB770}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4429A6A6-767C-4C3F-8298-BA35B9F5E904}">
   <dimension ref="B9:DH60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26051,7 +26051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1FF3C3-D0F6-4DD1-80A5-734930EF838C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C3E2833-F934-4108-84F8-F4CE9C1FAD19}">
   <dimension ref="B9:E34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26417,7 +26417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C1C5AA-C71A-4381-8190-1561AAEDB0F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE302C02-7623-418F-B8AD-5227929C40E7}">
   <dimension ref="B9:D58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26972,7 +26972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{134034F6-DE9C-4549-8EFE-37AF0CE8B888}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C51C49-10AE-417E-9187-6C41D4FFF56B}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27263,7 +27263,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F04EA5C-245D-4EC3-AC5F-9AE10A8ADA6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147F3F49-4329-4F87-BD95-151AFAB1CAFD}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27309,7 +27309,7 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>0.17526666666666665</v>
+        <v>0.17526666666666668</v>
       </c>
       <c r="E12" t="s">
         <v>201</v>
@@ -27351,7 +27351,7 @@
         <v>37</v>
       </c>
       <c r="D15">
-        <v>0.20653333333333332</v>
+        <v>0.20653333333333335</v>
       </c>
       <c r="E15" t="s">
         <v>201</v>
@@ -27435,7 +27435,7 @@
         <v>43</v>
       </c>
       <c r="D21">
-        <v>0.12036666666666666</v>
+        <v>0.12036666666666668</v>
       </c>
       <c r="E21" t="s">
         <v>201</v>
@@ -27491,7 +27491,7 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>0.24466666666666667</v>
+        <v>0.2446666666666667</v>
       </c>
       <c r="E25" t="s">
         <v>201</v>
@@ -27673,7 +27673,7 @@
         <v>45</v>
       </c>
       <c r="D38">
-        <v>0.20659999999999998</v>
+        <v>0.20660000000000001</v>
       </c>
       <c r="E38" t="s">
         <v>201</v>
@@ -27729,7 +27729,7 @@
         <v>45</v>
       </c>
       <c r="D42">
-        <v>0.29533333333333339</v>
+        <v>0.29533333333333334</v>
       </c>
       <c r="E42" t="s">
         <v>201</v>
@@ -27785,7 +27785,7 @@
         <v>45</v>
       </c>
       <c r="D46">
-        <v>0.22879999999999998</v>
+        <v>0.2288</v>
       </c>
       <c r="E46" t="s">
         <v>201</v>
@@ -27799,7 +27799,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="E47" t="s">
         <v>201</v>
@@ -27841,7 +27841,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.24779999999999999</v>
+        <v>0.24780000000000002</v>
       </c>
       <c r="E50" t="s">
         <v>201</v>
@@ -27869,7 +27869,7 @@
         <v>41</v>
       </c>
       <c r="D52">
-        <v>0.32276666666666665</v>
+        <v>0.3227666666666667</v>
       </c>
       <c r="E52" t="s">
         <v>201</v>
@@ -27897,7 +27897,7 @@
         <v>45</v>
       </c>
       <c r="D54">
-        <v>0.22766666666666668</v>
+        <v>0.22766666666666666</v>
       </c>
       <c r="E54" t="s">
         <v>201</v>
@@ -27939,7 +27939,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.18733333333333332</v>
+        <v>0.18733333333333335</v>
       </c>
       <c r="E57" t="s">
         <v>201</v>
@@ -27967,7 +27967,7 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="E59" t="s">
         <v>201</v>
@@ -28037,7 +28037,7 @@
         <v>41</v>
       </c>
       <c r="D64">
-        <v>0.3297666666666666</v>
+        <v>0.32976666666666665</v>
       </c>
       <c r="E64" t="s">
         <v>201</v>
@@ -28051,7 +28051,7 @@
         <v>43</v>
       </c>
       <c r="D65">
-        <v>0.20076666666666668</v>
+        <v>0.20076666666666665</v>
       </c>
       <c r="E65" t="s">
         <v>201</v>
@@ -28065,7 +28065,7 @@
         <v>45</v>
       </c>
       <c r="D66">
-        <v>0.19193333333333332</v>
+        <v>0.19193333333333337</v>
       </c>
       <c r="E66" t="s">
         <v>201</v>
@@ -28079,7 +28079,7 @@
         <v>37</v>
       </c>
       <c r="D67">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="E67" t="s">
         <v>201</v>
@@ -28121,7 +28121,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.27233333333333337</v>
+        <v>0.27233333333333332</v>
       </c>
       <c r="E70" t="s">
         <v>201</v>
@@ -28247,7 +28247,7 @@
         <v>37</v>
       </c>
       <c r="D79">
-        <v>0.3242666666666667</v>
+        <v>0.32426666666666665</v>
       </c>
       <c r="E79" t="s">
         <v>201</v>
@@ -28303,7 +28303,7 @@
         <v>37</v>
       </c>
       <c r="D83">
-        <v>0.30743333333333334</v>
+        <v>0.30743333333333328</v>
       </c>
       <c r="E83" t="s">
         <v>201</v>
@@ -28415,7 +28415,7 @@
         <v>37</v>
       </c>
       <c r="D91">
-        <v>0.3143333333333333</v>
+        <v>0.31433333333333335</v>
       </c>
       <c r="E91" t="s">
         <v>201</v>
@@ -28429,7 +28429,7 @@
         <v>41</v>
       </c>
       <c r="D92">
-        <v>0.31546666666666667</v>
+        <v>0.31546666666666673</v>
       </c>
       <c r="E92" t="s">
         <v>201</v>
@@ -28457,7 +28457,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.21929999999999997</v>
+        <v>0.21930000000000002</v>
       </c>
       <c r="E94" t="s">
         <v>201</v>
@@ -28611,7 +28611,7 @@
         <v>43</v>
       </c>
       <c r="D105">
-        <v>0.1952666666666667</v>
+        <v>0.19526666666666667</v>
       </c>
       <c r="E105" t="s">
         <v>201</v>
@@ -28625,7 +28625,7 @@
         <v>45</v>
       </c>
       <c r="D106">
-        <v>0.17756666666666665</v>
+        <v>0.17756666666666668</v>
       </c>
       <c r="E106" t="s">
         <v>201</v>
@@ -28653,7 +28653,7 @@
         <v>41</v>
       </c>
       <c r="D108">
-        <v>0.32569999999999999</v>
+        <v>0.32569999999999993</v>
       </c>
       <c r="E108" t="s">
         <v>201</v>
@@ -28695,7 +28695,7 @@
         <v>37</v>
       </c>
       <c r="D111">
-        <v>0.31429999999999997</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="E111" t="s">
         <v>201</v>
@@ -28807,7 +28807,7 @@
         <v>37</v>
       </c>
       <c r="D119">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="E119" t="s">
         <v>201</v>
@@ -28877,7 +28877,7 @@
         <v>41</v>
       </c>
       <c r="D124">
-        <v>0.3557333333333334</v>
+        <v>0.35573333333333329</v>
       </c>
       <c r="E124" t="s">
         <v>201</v>
@@ -28905,7 +28905,7 @@
         <v>45</v>
       </c>
       <c r="D126">
-        <v>0.21530000000000002</v>
+        <v>0.21529999999999996</v>
       </c>
       <c r="E126" t="s">
         <v>201</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99BA612D-6185-49A1-8D4B-39A1E8D4BC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7A12420-FE60-4429-A0D7-1E5DF532FF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -621,13 +621,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH03,S01aH04,S02aH03,S03aH02,S03aH05,S04aH02,S01aH02,S04aH04,S03aH04,S03aH03,S01aH03,S02aH02,S04aH05,S01aH05,S02aH04,S02aH05</t>
+    <t>S03aH04,S03aH02,S01aH02,S04aH04,S03aH05,S04aH03,S02aH04,S02aH05,S03aH03,S04aH05,S01aH05,S01aH04,S01aH03,S02aH02,S04aH02,S02aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH01,S01aH01,S04aH01,S04aH06,S03aH06,S03aH01,S01aH06,S02aH06</t>
+    <t>S03aH06,S02aH01,S02aH06,S03aH01,S01aH01,S04aH01,S04aH06,S01aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH01,S01aH01,S04aH01,S04aH06,S03aH06,S03aH01,S01aH06,S02aH06</v>
+        <v>S03aH06,S02aH01,S02aH06,S03aH01,S01aH01,S04aH01,S04aH06,S01aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S04aH03,S01aH04,S02aH03,S03aH02,S03aH05,S04aH02,S01aH02,S04aH04,S03aH04,S03aH03,S01aH03,S02aH02,S04aH05,S01aH05,S02aH04,S02aH05</v>
+        <v>S03aH04,S03aH02,S01aH02,S04aH04,S03aH05,S04aH03,S02aH04,S02aH05,S03aH03,S04aH05,S01aH05,S01aH04,S01aH03,S02aH02,S04aH02,S02aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1350,7 +1350,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4612908-28BC-4D55-B9B8-A1E4D1F94813}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1058218F-9110-4FEF-9650-5603E259C6BB}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1456,7 +1456,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE41091-0AD1-4372-9867-C36866FE65A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DB93C48-0385-4344-AB51-1019F9D6CAE7}">
   <dimension ref="B9:O490"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16878,7 +16878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4429A6A6-767C-4C3F-8298-BA35B9F5E904}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59992783-EA56-463E-841E-970C6C69009D}">
   <dimension ref="B9:DH60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26051,7 +26051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C3E2833-F934-4108-84F8-F4CE9C1FAD19}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{993508E7-F7CD-43F7-9803-4233268429B1}">
   <dimension ref="B9:E34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26417,7 +26417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE302C02-7623-418F-B8AD-5227929C40E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56EBC663-E987-4E91-90E2-D0505926DD55}">
   <dimension ref="B9:D58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26972,7 +26972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C51C49-10AE-417E-9187-6C41D4FFF56B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47852F15-5D35-4CD0-848F-D48C01A4E5C3}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27263,7 +27263,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147F3F49-4329-4F87-BD95-151AFAB1CAFD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB068BD-47F6-4109-A4CC-9C836C6BE4F6}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27407,7 +27407,7 @@
         <v>37</v>
       </c>
       <c r="D19">
-        <v>0.23840000000000003</v>
+        <v>0.23839999999999997</v>
       </c>
       <c r="E19" t="s">
         <v>201</v>
@@ -27421,7 +27421,7 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>0.23150000000000001</v>
+        <v>0.23149999999999996</v>
       </c>
       <c r="E20" t="s">
         <v>201</v>
@@ -27645,7 +27645,7 @@
         <v>41</v>
       </c>
       <c r="D36">
-        <v>0.32773333333333338</v>
+        <v>0.32773333333333332</v>
       </c>
       <c r="E36" t="s">
         <v>201</v>
@@ -27673,7 +27673,7 @@
         <v>45</v>
       </c>
       <c r="D38">
-        <v>0.20660000000000001</v>
+        <v>0.20659999999999998</v>
       </c>
       <c r="E38" t="s">
         <v>201</v>
@@ -27729,7 +27729,7 @@
         <v>45</v>
       </c>
       <c r="D42">
-        <v>0.29533333333333334</v>
+        <v>0.29533333333333339</v>
       </c>
       <c r="E42" t="s">
         <v>201</v>
@@ -27757,7 +27757,7 @@
         <v>41</v>
       </c>
       <c r="D44">
-        <v>0.34233333333333338</v>
+        <v>0.34233333333333332</v>
       </c>
       <c r="E44" t="s">
         <v>201</v>
@@ -27785,7 +27785,7 @@
         <v>45</v>
       </c>
       <c r="D46">
-        <v>0.2288</v>
+        <v>0.22879999999999998</v>
       </c>
       <c r="E46" t="s">
         <v>201</v>
@@ -27799,7 +27799,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="E47" t="s">
         <v>201</v>
@@ -27841,7 +27841,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.24780000000000002</v>
+        <v>0.24779999999999999</v>
       </c>
       <c r="E50" t="s">
         <v>201</v>
@@ -27855,7 +27855,7 @@
         <v>37</v>
       </c>
       <c r="D51">
-        <v>0.31676666666666664</v>
+        <v>0.3167666666666667</v>
       </c>
       <c r="E51" t="s">
         <v>201</v>
@@ -27897,7 +27897,7 @@
         <v>45</v>
       </c>
       <c r="D54">
-        <v>0.22766666666666666</v>
+        <v>0.22766666666666668</v>
       </c>
       <c r="E54" t="s">
         <v>201</v>
@@ -27925,7 +27925,7 @@
         <v>41</v>
       </c>
       <c r="D56">
-        <v>0.35000000000000003</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="E56" t="s">
         <v>201</v>
@@ -27967,7 +27967,7 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="E59" t="s">
         <v>201</v>
@@ -28037,7 +28037,7 @@
         <v>41</v>
       </c>
       <c r="D64">
-        <v>0.32976666666666665</v>
+        <v>0.3297666666666666</v>
       </c>
       <c r="E64" t="s">
         <v>201</v>
@@ -28065,7 +28065,7 @@
         <v>45</v>
       </c>
       <c r="D66">
-        <v>0.19193333333333337</v>
+        <v>0.19193333333333332</v>
       </c>
       <c r="E66" t="s">
         <v>201</v>
@@ -28079,7 +28079,7 @@
         <v>37</v>
       </c>
       <c r="D67">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="E67" t="s">
         <v>201</v>
@@ -28093,7 +28093,7 @@
         <v>41</v>
       </c>
       <c r="D68">
-        <v>0.38203333333333328</v>
+        <v>0.38203333333333339</v>
       </c>
       <c r="E68" t="s">
         <v>201</v>
@@ -28121,7 +28121,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.27233333333333332</v>
+        <v>0.27233333333333337</v>
       </c>
       <c r="E70" t="s">
         <v>201</v>
@@ -28317,7 +28317,7 @@
         <v>41</v>
       </c>
       <c r="D84">
-        <v>0.3323666666666667</v>
+        <v>0.33236666666666664</v>
       </c>
       <c r="E84" t="s">
         <v>201</v>
@@ -28457,7 +28457,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.21930000000000002</v>
+        <v>0.21929999999999997</v>
       </c>
       <c r="E94" t="s">
         <v>201</v>
@@ -28583,7 +28583,7 @@
         <v>37</v>
       </c>
       <c r="D103">
-        <v>0.28610000000000002</v>
+        <v>0.28609999999999997</v>
       </c>
       <c r="E103" t="s">
         <v>201</v>
@@ -28597,7 +28597,7 @@
         <v>41</v>
       </c>
       <c r="D104">
-        <v>0.32653333333333329</v>
+        <v>0.32653333333333334</v>
       </c>
       <c r="E104" t="s">
         <v>201</v>
@@ -28625,7 +28625,7 @@
         <v>45</v>
       </c>
       <c r="D106">
-        <v>0.17756666666666668</v>
+        <v>0.17756666666666665</v>
       </c>
       <c r="E106" t="s">
         <v>201</v>
@@ -28639,7 +28639,7 @@
         <v>37</v>
       </c>
       <c r="D107">
-        <v>0.32646666666666663</v>
+        <v>0.32646666666666668</v>
       </c>
       <c r="E107" t="s">
         <v>201</v>
@@ -28765,7 +28765,7 @@
         <v>41</v>
       </c>
       <c r="D116">
-        <v>0.32293333333333335</v>
+        <v>0.32293333333333329</v>
       </c>
       <c r="E116" t="s">
         <v>201</v>
@@ -28807,7 +28807,7 @@
         <v>37</v>
       </c>
       <c r="D119">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="E119" t="s">
         <v>201</v>
@@ -28863,7 +28863,7 @@
         <v>37</v>
       </c>
       <c r="D123">
-        <v>0.30760000000000004</v>
+        <v>0.30759999999999998</v>
       </c>
       <c r="E123" t="s">
         <v>201</v>
@@ -28877,7 +28877,7 @@
         <v>41</v>
       </c>
       <c r="D124">
-        <v>0.35573333333333329</v>
+        <v>0.3557333333333334</v>
       </c>
       <c r="E124" t="s">
         <v>201</v>
@@ -28905,7 +28905,7 @@
         <v>45</v>
       </c>
       <c r="D126">
-        <v>0.21529999999999996</v>
+        <v>0.21530000000000002</v>
       </c>
       <c r="E126" t="s">
         <v>201</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7A12420-FE60-4429-A0D7-1E5DF532FF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7FC67E5-49DE-4DB4-BF63-10AD18F60BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -621,13 +621,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH04,S03aH02,S01aH02,S04aH04,S03aH05,S04aH03,S02aH04,S02aH05,S03aH03,S04aH05,S01aH05,S01aH04,S01aH03,S02aH02,S04aH02,S02aH03</t>
+    <t>S03aH05,S02aH03,S03aH02,S04aH03,S03aH03,S01aH04,S04aH05,S01aH05,S02aH02,S03aH04,S01aH03,S04aH02,S01aH02,S04aH04,S02aH04,S02aH05</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH06,S02aH01,S02aH06,S03aH01,S01aH01,S04aH01,S04aH06,S01aH06</t>
+    <t>S01aH01,S04aH01,S04aH06,S02aH01,S03aH01,S03aH06,S02aH06,S01aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH06,S02aH01,S02aH06,S03aH01,S01aH01,S04aH01,S04aH06,S01aH06</v>
+        <v>S01aH01,S04aH01,S04aH06,S02aH01,S03aH01,S03aH06,S02aH06,S01aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH04,S03aH02,S01aH02,S04aH04,S03aH05,S04aH03,S02aH04,S02aH05,S03aH03,S04aH05,S01aH05,S01aH04,S01aH03,S02aH02,S04aH02,S02aH03</v>
+        <v>S03aH05,S02aH03,S03aH02,S04aH03,S03aH03,S01aH04,S04aH05,S01aH05,S02aH02,S03aH04,S01aH03,S04aH02,S01aH02,S04aH04,S02aH04,S02aH05</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1350,7 +1350,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1058218F-9110-4FEF-9650-5603E259C6BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C46099D-9F0F-4E1D-AE2E-0301873F718D}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1456,7 +1456,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DB93C48-0385-4344-AB51-1019F9D6CAE7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D06A198-37ED-4A70-83DE-AB040B283552}">
   <dimension ref="B9:O490"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16878,7 +16878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59992783-EA56-463E-841E-970C6C69009D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00CA09F9-4DC5-46D2-B35C-3CC7CC5BE1F7}">
   <dimension ref="B9:DH60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26051,7 +26051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{993508E7-F7CD-43F7-9803-4233268429B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D9FCD11-BE99-47C1-9502-8FD418F795A9}">
   <dimension ref="B9:E34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26417,7 +26417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56EBC663-E987-4E91-90E2-D0505926DD55}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118A2D40-9626-449B-8F91-BAA045BC6891}">
   <dimension ref="B9:D58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26972,7 +26972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47852F15-5D35-4CD0-848F-D48C01A4E5C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632199B1-AAB9-4269-87AF-8136AB0C801E}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27263,7 +27263,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB068BD-47F6-4109-A4CC-9C836C6BE4F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B8E9855-90AD-4BF5-8002-BC094CBA8EAC}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27309,7 +27309,7 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>0.17526666666666668</v>
+        <v>0.17526666666666665</v>
       </c>
       <c r="E12" t="s">
         <v>201</v>
@@ -27337,7 +27337,7 @@
         <v>45</v>
       </c>
       <c r="D14">
-        <v>0.19109999999999996</v>
+        <v>0.19110000000000002</v>
       </c>
       <c r="E14" t="s">
         <v>201</v>
@@ -27421,7 +27421,7 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>0.23149999999999996</v>
+        <v>0.23150000000000001</v>
       </c>
       <c r="E20" t="s">
         <v>201</v>
@@ -27491,7 +27491,7 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>0.2446666666666667</v>
+        <v>0.24466666666666667</v>
       </c>
       <c r="E25" t="s">
         <v>201</v>
@@ -27645,7 +27645,7 @@
         <v>41</v>
       </c>
       <c r="D36">
-        <v>0.32773333333333332</v>
+        <v>0.32773333333333338</v>
       </c>
       <c r="E36" t="s">
         <v>201</v>
@@ -27673,7 +27673,7 @@
         <v>45</v>
       </c>
       <c r="D38">
-        <v>0.20659999999999998</v>
+        <v>0.20660000000000001</v>
       </c>
       <c r="E38" t="s">
         <v>201</v>
@@ -27729,7 +27729,7 @@
         <v>45</v>
       </c>
       <c r="D42">
-        <v>0.29533333333333339</v>
+        <v>0.29533333333333334</v>
       </c>
       <c r="E42" t="s">
         <v>201</v>
@@ -27757,7 +27757,7 @@
         <v>41</v>
       </c>
       <c r="D44">
-        <v>0.34233333333333332</v>
+        <v>0.34233333333333338</v>
       </c>
       <c r="E44" t="s">
         <v>201</v>
@@ -27785,7 +27785,7 @@
         <v>45</v>
       </c>
       <c r="D46">
-        <v>0.22879999999999998</v>
+        <v>0.2288</v>
       </c>
       <c r="E46" t="s">
         <v>201</v>
@@ -27869,7 +27869,7 @@
         <v>41</v>
       </c>
       <c r="D52">
-        <v>0.3227666666666667</v>
+        <v>0.32276666666666665</v>
       </c>
       <c r="E52" t="s">
         <v>201</v>
@@ -27925,7 +27925,7 @@
         <v>41</v>
       </c>
       <c r="D56">
-        <v>0.34999999999999992</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="E56" t="s">
         <v>201</v>
@@ -27939,7 +27939,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.18733333333333335</v>
+        <v>0.18733333333333332</v>
       </c>
       <c r="E57" t="s">
         <v>201</v>
@@ -27995,7 +27995,7 @@
         <v>43</v>
       </c>
       <c r="D61">
-        <v>0.20516666666666664</v>
+        <v>0.20516666666666669</v>
       </c>
       <c r="E61" t="s">
         <v>201</v>
@@ -28051,7 +28051,7 @@
         <v>43</v>
       </c>
       <c r="D65">
-        <v>0.20076666666666665</v>
+        <v>0.20076666666666668</v>
       </c>
       <c r="E65" t="s">
         <v>201</v>
@@ -28065,7 +28065,7 @@
         <v>45</v>
       </c>
       <c r="D66">
-        <v>0.19193333333333332</v>
+        <v>0.19193333333333337</v>
       </c>
       <c r="E66" t="s">
         <v>201</v>
@@ -28093,7 +28093,7 @@
         <v>41</v>
       </c>
       <c r="D68">
-        <v>0.38203333333333339</v>
+        <v>0.38203333333333328</v>
       </c>
       <c r="E68" t="s">
         <v>201</v>
@@ -28121,7 +28121,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.27233333333333337</v>
+        <v>0.27233333333333332</v>
       </c>
       <c r="E70" t="s">
         <v>201</v>
@@ -28163,7 +28163,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.19603333333333331</v>
+        <v>0.19603333333333336</v>
       </c>
       <c r="E73" t="s">
         <v>201</v>
@@ -28219,7 +28219,7 @@
         <v>43</v>
       </c>
       <c r="D77">
-        <v>0.21280000000000002</v>
+        <v>0.21279999999999999</v>
       </c>
       <c r="E77" t="s">
         <v>201</v>
@@ -28317,7 +28317,7 @@
         <v>41</v>
       </c>
       <c r="D84">
-        <v>0.33236666666666664</v>
+        <v>0.3323666666666667</v>
       </c>
       <c r="E84" t="s">
         <v>201</v>
@@ -28429,7 +28429,7 @@
         <v>41</v>
       </c>
       <c r="D92">
-        <v>0.31546666666666673</v>
+        <v>0.31546666666666667</v>
       </c>
       <c r="E92" t="s">
         <v>201</v>
@@ -28597,7 +28597,7 @@
         <v>41</v>
       </c>
       <c r="D104">
-        <v>0.32653333333333334</v>
+        <v>0.32653333333333329</v>
       </c>
       <c r="E104" t="s">
         <v>201</v>
@@ -28625,7 +28625,7 @@
         <v>45</v>
       </c>
       <c r="D106">
-        <v>0.17756666666666665</v>
+        <v>0.17756666666666668</v>
       </c>
       <c r="E106" t="s">
         <v>201</v>
@@ -28653,7 +28653,7 @@
         <v>41</v>
       </c>
       <c r="D108">
-        <v>0.32569999999999993</v>
+        <v>0.32569999999999999</v>
       </c>
       <c r="E108" t="s">
         <v>201</v>
@@ -28765,7 +28765,7 @@
         <v>41</v>
       </c>
       <c r="D116">
-        <v>0.32293333333333329</v>
+        <v>0.32293333333333335</v>
       </c>
       <c r="E116" t="s">
         <v>201</v>
@@ -28849,7 +28849,7 @@
         <v>45</v>
       </c>
       <c r="D122">
-        <v>0.23020000000000004</v>
+        <v>0.23019999999999999</v>
       </c>
       <c r="E122" t="s">
         <v>201</v>
@@ -28891,7 +28891,7 @@
         <v>43</v>
       </c>
       <c r="D125">
-        <v>0.17353333333333332</v>
+        <v>0.17353333333333334</v>
       </c>
       <c r="E125" t="s">
         <v>201</v>
@@ -28905,7 +28905,7 @@
         <v>45</v>
       </c>
       <c r="D126">
-        <v>0.21530000000000002</v>
+        <v>0.21529999999999996</v>
       </c>
       <c r="E126" t="s">
         <v>201</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9AF8799-8D57-480B-8E2F-AC2016E9E986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B38BD6F-6CFE-4D8A-9237-B1D6362DF0FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -624,13 +624,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH02,S02aH03,S03aH04,S03aH02,S04aH02,S03aH05,S03aH03,S04aH05,S01aH04,S01aH02,S04aH04,S02aH04,S02aH05,S01aH03,S01aH05,S04aH03</t>
+    <t>S04aH03,S04aH05,S03aH02,S03aH03,S02aH03,S01aH05,S01aH03,S03aH04,S01aH02,S04aH04,S03aH05,S01aH04,S02aH04,S02aH05,S02aH02,S04aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S01aH01,S04aH01,S04aH06,S03aH06,S02aH06,S01aH06,S02aH01</t>
+    <t>S02aH01,S01aH01,S04aH01,S04aH06,S03aH06,S02aH06,S03aH01,S01aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -915,7 +915,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F262B48-54BF-514B-23DA-39FB34284191}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77054B2E-625D-05F8-CFCD-4BF004E32365}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -970,7 +970,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AC3A947-2711-A719-2213-6A70525903D3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D199258A-7287-4C26-7DDF-CB303B0348C3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1025,7 +1025,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AE3664B-2EF9-C86B-DA3B-BAF076124858}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BB5D02E-F08A-3D06-2817-A75ACF6CAB9E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1080,7 +1080,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BECA5707-05D6-D0ED-43EF-B3243FE8608C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C89C7660-D052-9EA3-923D-9BF743F07F0D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1135,7 +1135,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21E3B6B4-016C-74D3-640F-EEFCA316DAA8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{865A6552-7D87-1D3D-7412-2AD149D40C4F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1190,7 +1190,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C2E988A-36D7-AE9D-8F43-4FB947D2350E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CC94658-4C77-4632-EF6D-57E9DF9215AC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1245,7 +1245,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E39E9935-DB69-D93C-C92D-F0C9E5634F33}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC783A6D-B65E-A627-6CF0-78F12F79ABFD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1300,7 +1300,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1358DFB-8D80-C187-0053-6C446503016B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F2155AA-1AB0-AF6C-60D7-E2A1A0EB8CEB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH01,S01aH01,S04aH01,S04aH06,S03aH06,S02aH06,S01aH06,S02aH01</v>
+        <v>S02aH01,S01aH01,S04aH01,S04aH06,S03aH06,S02aH06,S03aH01,S01aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH02,S02aH03,S03aH04,S03aH02,S04aH02,S03aH05,S03aH03,S04aH05,S01aH04,S01aH02,S04aH04,S02aH04,S02aH05,S01aH03,S01aH05,S04aH03</v>
+        <v>S04aH03,S04aH05,S03aH02,S03aH03,S02aH03,S01aH05,S01aH03,S03aH04,S01aH02,S04aH04,S03aH05,S01aH04,S02aH04,S02aH05,S02aH02,S04aH02</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1916,7 +1916,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{695837A2-732B-424D-932C-900ADEDEC447}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B8B713E-6AC5-4800-A3FA-E6479981BC29}">
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2055,7 +2055,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AE934DD-11C7-49A4-B9B3-FE21D7E2B3D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB4F799D-0E2C-4A6E-AE09-286B19B84A74}">
   <dimension ref="A1:O490"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -17501,7 +17501,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83E13438-7CF2-477B-8F13-D6B191B6336B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C531363-80EC-4CE5-AAC8-1925E72A6F1F}">
   <dimension ref="A1:DH60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -26723,7 +26723,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0E55C3-5A9C-4A40-93A5-229F044A3680}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0336389C-B7E6-4CB2-9E4C-4CCF05D98C30}">
   <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -27109,7 +27109,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AACD527-CAED-4D8B-B402-0416C9FBAEDB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ADDDDD3-1039-422E-97A4-37EC80889BB2}">
   <dimension ref="A1:H58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -27684,7 +27684,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C51DE30-7F00-48EC-A4ED-5BB182B1CDFE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51A689CD-54E6-49B2-BA4B-1FA897996E9F}">
   <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -27995,7 +27995,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A618EAEC-3F42-46CE-89E9-E12717D2D322}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C55A20-A57E-4818-B99B-C61575DC2CD8}">
   <dimension ref="A1:H126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -28056,7 +28056,7 @@
         <v>41</v>
       </c>
       <c r="D12" s="24">
-        <v>0.17526666666666665</v>
+        <v>0.17526666666666668</v>
       </c>
       <c r="E12" s="23" t="s">
         <v>202</v>
@@ -28154,7 +28154,7 @@
         <v>37</v>
       </c>
       <c r="D19" s="21">
-        <v>0.23840000000000003</v>
+        <v>0.23839999999999997</v>
       </c>
       <c r="E19" s="20" t="s">
         <v>202</v>
@@ -28238,7 +28238,7 @@
         <v>43</v>
       </c>
       <c r="D25" s="21">
-        <v>0.2446666666666667</v>
+        <v>0.24466666666666667</v>
       </c>
       <c r="E25" s="20" t="s">
         <v>202</v>
@@ -28546,7 +28546,7 @@
         <v>37</v>
       </c>
       <c r="D47" s="21">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="E47" s="20" t="s">
         <v>202</v>
@@ -28602,7 +28602,7 @@
         <v>37</v>
       </c>
       <c r="D51" s="21">
-        <v>0.31676666666666664</v>
+        <v>0.3167666666666667</v>
       </c>
       <c r="E51" s="20" t="s">
         <v>202</v>
@@ -28616,7 +28616,7 @@
         <v>41</v>
       </c>
       <c r="D52" s="24">
-        <v>0.32276666666666665</v>
+        <v>0.3227666666666667</v>
       </c>
       <c r="E52" s="23" t="s">
         <v>202</v>
@@ -28686,7 +28686,7 @@
         <v>43</v>
       </c>
       <c r="D57" s="21">
-        <v>0.18733333333333335</v>
+        <v>0.18733333333333332</v>
       </c>
       <c r="E57" s="20" t="s">
         <v>202</v>
@@ -28714,7 +28714,7 @@
         <v>37</v>
       </c>
       <c r="D59" s="21">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="E59" s="20" t="s">
         <v>202</v>
@@ -28742,7 +28742,7 @@
         <v>43</v>
       </c>
       <c r="D61" s="21">
-        <v>0.20516666666666664</v>
+        <v>0.20516666666666669</v>
       </c>
       <c r="E61" s="20" t="s">
         <v>202</v>
@@ -28784,7 +28784,7 @@
         <v>41</v>
       </c>
       <c r="D64" s="24">
-        <v>0.3297666666666666</v>
+        <v>0.32976666666666665</v>
       </c>
       <c r="E64" s="23" t="s">
         <v>202</v>
@@ -28798,7 +28798,7 @@
         <v>43</v>
       </c>
       <c r="D65" s="21">
-        <v>0.20076666666666665</v>
+        <v>0.20076666666666668</v>
       </c>
       <c r="E65" s="20" t="s">
         <v>202</v>
@@ -28826,7 +28826,7 @@
         <v>37</v>
       </c>
       <c r="D67" s="21">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="E67" s="20" t="s">
         <v>202</v>
@@ -28910,7 +28910,7 @@
         <v>43</v>
       </c>
       <c r="D73" s="21">
-        <v>0.19603333333333331</v>
+        <v>0.19603333333333336</v>
       </c>
       <c r="E73" s="20" t="s">
         <v>202</v>
@@ -28966,7 +28966,7 @@
         <v>43</v>
       </c>
       <c r="D77" s="21">
-        <v>0.21280000000000002</v>
+        <v>0.21279999999999999</v>
       </c>
       <c r="E77" s="20" t="s">
         <v>202</v>
@@ -29176,7 +29176,7 @@
         <v>41</v>
       </c>
       <c r="D92" s="24">
-        <v>0.31546666666666667</v>
+        <v>0.31546666666666673</v>
       </c>
       <c r="E92" s="23" t="s">
         <v>202</v>
@@ -29330,7 +29330,7 @@
         <v>37</v>
       </c>
       <c r="D103" s="21">
-        <v>0.28610000000000002</v>
+        <v>0.28609999999999997</v>
       </c>
       <c r="E103" s="20" t="s">
         <v>202</v>
@@ -29386,7 +29386,7 @@
         <v>37</v>
       </c>
       <c r="D107" s="21">
-        <v>0.32646666666666663</v>
+        <v>0.32646666666666668</v>
       </c>
       <c r="E107" s="20" t="s">
         <v>202</v>
@@ -29400,7 +29400,7 @@
         <v>41</v>
       </c>
       <c r="D108" s="24">
-        <v>0.32569999999999999</v>
+        <v>0.32569999999999993</v>
       </c>
       <c r="E108" s="23" t="s">
         <v>202</v>
@@ -29554,7 +29554,7 @@
         <v>37</v>
       </c>
       <c r="D119" s="21">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="E119" s="20" t="s">
         <v>202</v>
@@ -29610,7 +29610,7 @@
         <v>37</v>
       </c>
       <c r="D123" s="21">
-        <v>0.30760000000000004</v>
+        <v>0.30759999999999998</v>
       </c>
       <c r="E123" s="20" t="s">
         <v>202</v>
@@ -29624,7 +29624,7 @@
         <v>41</v>
       </c>
       <c r="D124" s="24">
-        <v>0.3557333333333334</v>
+        <v>0.35573333333333329</v>
       </c>
       <c r="E124" s="23" t="s">
         <v>202</v>
@@ -29638,7 +29638,7 @@
         <v>43</v>
       </c>
       <c r="D125" s="21">
-        <v>0.17353333333333332</v>
+        <v>0.17353333333333334</v>
       </c>
       <c r="E125" s="20" t="s">
         <v>202</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A06D26F-84A8-41D1-9F43-EB73CAC15FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6CF90D4-E3B7-4E3D-89B8-140CC0243749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -621,13 +621,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH05,S01aH03,S03aH05,S03aH04,S02aH02,S02aH03,S04aH03,S02aH04,S02aH05,S01aH02,S04aH04,S04aH02,S04aH05,S01aH04,S03aH03,S03aH02</t>
+    <t>S01aH04,S01aH03,S04aH05,S03aH04,S02aH02,S01aH05,S02aH03,S01aH02,S04aH04,S03aH05,S04aH03,S03aH02,S02aH04,S02aH05,S03aH03,S04aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S01aH01,S04aH01,S04aH06,S01aH06,S02aH01,S02aH06,S03aH06</t>
+    <t>S03aH01,S01aH01,S04aH01,S04aH06,S03aH06,S02aH01,S01aH06,S02aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH01,S01aH01,S04aH01,S04aH06,S01aH06,S02aH01,S02aH06,S03aH06</v>
+        <v>S03aH01,S01aH01,S04aH01,S04aH06,S03aH06,S02aH01,S01aH06,S02aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH05,S01aH03,S03aH05,S03aH04,S02aH02,S02aH03,S04aH03,S02aH04,S02aH05,S01aH02,S04aH04,S04aH02,S04aH05,S01aH04,S03aH03,S03aH02</v>
+        <v>S01aH04,S01aH03,S04aH05,S03aH04,S02aH02,S01aH05,S02aH03,S01aH02,S04aH04,S03aH05,S04aH03,S03aH02,S02aH04,S02aH05,S03aH03,S04aH02</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1350,7 +1350,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{333CBB6B-041C-4A8B-B824-3E9A7A90AFD7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1FBF3AC-E02E-4AAC-A57E-5F5238C439CA}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1456,7 +1456,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD6D8010-BD92-4FD8-88E3-BE37CC2F77ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB1EE9B-8B9B-47F7-B5A9-0B91A57859B1}">
   <dimension ref="B9:O490"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16878,7 +16878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8FD9FE3-73CA-4327-A8D5-5F12EEB6FDF0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245CA453-20B8-42D1-B369-2B8D93056CBC}">
   <dimension ref="B9:DH60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26051,7 +26051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E03F09-2889-4CA5-8DE8-AF7B6858639C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1806A014-1F23-4E02-9C42-401BA955BE82}">
   <dimension ref="B9:E34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26417,7 +26417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C73E81DF-0210-4533-B2EF-ED06C00AB92D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9B74B83-F91A-42A0-9D1F-68C2CBADB9F0}">
   <dimension ref="B9:D58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26972,7 +26972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC7D455-4A3A-4533-9206-964F9DBFAC46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16DC3DDE-DB18-49B2-B3C0-8BEAE9FA1907}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27263,7 +27263,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CD70CF8-6991-4F37-8E27-3556CF129221}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8753E04-E29D-485E-8265-28B3FD62E2D0}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27351,7 +27351,7 @@
         <v>37</v>
       </c>
       <c r="D15">
-        <v>0.20653333333333332</v>
+        <v>0.20653333333333335</v>
       </c>
       <c r="E15" t="s">
         <v>201</v>
@@ -27421,7 +27421,7 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>0.23150000000000001</v>
+        <v>0.23149999999999996</v>
       </c>
       <c r="E20" t="s">
         <v>201</v>
@@ -27435,7 +27435,7 @@
         <v>43</v>
       </c>
       <c r="D21">
-        <v>0.12036666666666668</v>
+        <v>0.12036666666666666</v>
       </c>
       <c r="E21" t="s">
         <v>201</v>
@@ -27491,7 +27491,7 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>0.2446666666666667</v>
+        <v>0.24466666666666667</v>
       </c>
       <c r="E25" t="s">
         <v>201</v>
@@ -27645,7 +27645,7 @@
         <v>41</v>
       </c>
       <c r="D36">
-        <v>0.32773333333333338</v>
+        <v>0.32773333333333332</v>
       </c>
       <c r="E36" t="s">
         <v>201</v>
@@ -27757,7 +27757,7 @@
         <v>41</v>
       </c>
       <c r="D44">
-        <v>0.34233333333333338</v>
+        <v>0.34233333333333332</v>
       </c>
       <c r="E44" t="s">
         <v>201</v>
@@ -27799,7 +27799,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="E47" t="s">
         <v>201</v>
@@ -27925,7 +27925,7 @@
         <v>41</v>
       </c>
       <c r="D56">
-        <v>0.35000000000000003</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="E56" t="s">
         <v>201</v>
@@ -27939,7 +27939,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.18733333333333335</v>
+        <v>0.18733333333333332</v>
       </c>
       <c r="E57" t="s">
         <v>201</v>
@@ -27967,7 +27967,7 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="E59" t="s">
         <v>201</v>
@@ -28037,7 +28037,7 @@
         <v>41</v>
       </c>
       <c r="D64">
-        <v>0.32976666666666665</v>
+        <v>0.3297666666666666</v>
       </c>
       <c r="E64" t="s">
         <v>201</v>
@@ -28051,7 +28051,7 @@
         <v>43</v>
       </c>
       <c r="D65">
-        <v>0.20076666666666665</v>
+        <v>0.20076666666666668</v>
       </c>
       <c r="E65" t="s">
         <v>201</v>
@@ -28079,7 +28079,7 @@
         <v>37</v>
       </c>
       <c r="D67">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="E67" t="s">
         <v>201</v>
@@ -28093,7 +28093,7 @@
         <v>41</v>
       </c>
       <c r="D68">
-        <v>0.38203333333333328</v>
+        <v>0.38203333333333339</v>
       </c>
       <c r="E68" t="s">
         <v>201</v>
@@ -28247,7 +28247,7 @@
         <v>37</v>
       </c>
       <c r="D79">
-        <v>0.3242666666666667</v>
+        <v>0.32426666666666665</v>
       </c>
       <c r="E79" t="s">
         <v>201</v>
@@ -28303,7 +28303,7 @@
         <v>37</v>
       </c>
       <c r="D83">
-        <v>0.30743333333333334</v>
+        <v>0.30743333333333328</v>
       </c>
       <c r="E83" t="s">
         <v>201</v>
@@ -28317,7 +28317,7 @@
         <v>41</v>
       </c>
       <c r="D84">
-        <v>0.3323666666666667</v>
+        <v>0.33236666666666664</v>
       </c>
       <c r="E84" t="s">
         <v>201</v>
@@ -28415,7 +28415,7 @@
         <v>37</v>
       </c>
       <c r="D91">
-        <v>0.3143333333333333</v>
+        <v>0.31433333333333335</v>
       </c>
       <c r="E91" t="s">
         <v>201</v>
@@ -28597,7 +28597,7 @@
         <v>41</v>
       </c>
       <c r="D104">
-        <v>0.32653333333333329</v>
+        <v>0.32653333333333334</v>
       </c>
       <c r="E104" t="s">
         <v>201</v>
@@ -28611,7 +28611,7 @@
         <v>43</v>
       </c>
       <c r="D105">
-        <v>0.19526666666666667</v>
+        <v>0.1952666666666667</v>
       </c>
       <c r="E105" t="s">
         <v>201</v>
@@ -28695,7 +28695,7 @@
         <v>37</v>
       </c>
       <c r="D111">
-        <v>0.31429999999999997</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="E111" t="s">
         <v>201</v>
@@ -28765,7 +28765,7 @@
         <v>41</v>
       </c>
       <c r="D116">
-        <v>0.32293333333333335</v>
+        <v>0.32293333333333329</v>
       </c>
       <c r="E116" t="s">
         <v>201</v>
@@ -28807,7 +28807,7 @@
         <v>37</v>
       </c>
       <c r="D119">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="E119" t="s">
         <v>201</v>
@@ -28877,7 +28877,7 @@
         <v>41</v>
       </c>
       <c r="D124">
-        <v>0.35573333333333329</v>
+        <v>0.3557333333333334</v>
       </c>
       <c r="E124" t="s">
         <v>201</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6CF90D4-E3B7-4E3D-89B8-140CC0243749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D780FAC-8452-4D6A-970D-9C2E21B2D1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -621,13 +621,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH04,S01aH03,S04aH05,S03aH04,S02aH02,S01aH05,S02aH03,S01aH02,S04aH04,S03aH05,S04aH03,S03aH02,S02aH04,S02aH05,S03aH03,S04aH02</t>
+    <t>S01aH04,S04aH03,S04aH02,S02aH03,S01aH02,S04aH04,S02aH02,S01aH03,S01aH05,S03aH03,S04aH05,S03aH05,S03aH04,S02aH04,S02aH05,S03aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S01aH01,S04aH01,S04aH06,S03aH06,S02aH01,S01aH06,S02aH06</t>
+    <t>S02aH01,S01aH01,S04aH01,S04aH06,S03aH06,S03aH01,S01aH06,S02aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH01,S01aH01,S04aH01,S04aH06,S03aH06,S02aH01,S01aH06,S02aH06</v>
+        <v>S02aH01,S01aH01,S04aH01,S04aH06,S03aH06,S03aH01,S01aH06,S02aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH04,S01aH03,S04aH05,S03aH04,S02aH02,S01aH05,S02aH03,S01aH02,S04aH04,S03aH05,S04aH03,S03aH02,S02aH04,S02aH05,S03aH03,S04aH02</v>
+        <v>S01aH04,S04aH03,S04aH02,S02aH03,S01aH02,S04aH04,S02aH02,S01aH03,S01aH05,S03aH03,S04aH05,S03aH05,S03aH04,S02aH04,S02aH05,S03aH02</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1350,7 +1350,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1FBF3AC-E02E-4AAC-A57E-5F5238C439CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3711339-E622-4B1E-AC94-EB2EA417B073}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1456,7 +1456,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB1EE9B-8B9B-47F7-B5A9-0B91A57859B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E380A8F-AE41-4A9D-8CA6-C3C70652A7AA}">
   <dimension ref="B9:O490"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16878,7 +16878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245CA453-20B8-42D1-B369-2B8D93056CBC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A00FBD1-665D-4F6B-AE6F-9263BBFCBAB2}">
   <dimension ref="B9:DH60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26051,7 +26051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1806A014-1F23-4E02-9C42-401BA955BE82}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{490BC121-4C6A-40EF-A6BD-288139276AE3}">
   <dimension ref="B9:E34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26417,7 +26417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9B74B83-F91A-42A0-9D1F-68C2CBADB9F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDECE10C-6289-47E0-828D-B311FC98CC61}">
   <dimension ref="B9:D58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26972,7 +26972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16DC3DDE-DB18-49B2-B3C0-8BEAE9FA1907}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5774204-6DE7-4079-8CE8-10967C8294C8}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27263,7 +27263,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8753E04-E29D-485E-8265-28B3FD62E2D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7769B53D-FFC0-4CA9-B08B-5E29887103AC}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27407,7 +27407,7 @@
         <v>37</v>
       </c>
       <c r="D19">
-        <v>0.23840000000000003</v>
+        <v>0.23839999999999997</v>
       </c>
       <c r="E19" t="s">
         <v>201</v>
@@ -27799,7 +27799,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="E47" t="s">
         <v>201</v>
@@ -27855,7 +27855,7 @@
         <v>37</v>
       </c>
       <c r="D51">
-        <v>0.31676666666666664</v>
+        <v>0.3167666666666667</v>
       </c>
       <c r="E51" t="s">
         <v>201</v>
@@ -27967,7 +27967,7 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="E59" t="s">
         <v>201</v>
@@ -28079,7 +28079,7 @@
         <v>37</v>
       </c>
       <c r="D67">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="E67" t="s">
         <v>201</v>
@@ -28583,7 +28583,7 @@
         <v>37</v>
       </c>
       <c r="D103">
-        <v>0.28610000000000002</v>
+        <v>0.28609999999999997</v>
       </c>
       <c r="E103" t="s">
         <v>201</v>
@@ -28639,7 +28639,7 @@
         <v>37</v>
       </c>
       <c r="D107">
-        <v>0.32646666666666663</v>
+        <v>0.32646666666666668</v>
       </c>
       <c r="E107" t="s">
         <v>201</v>
@@ -28807,7 +28807,7 @@
         <v>37</v>
       </c>
       <c r="D119">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="E119" t="s">
         <v>201</v>
@@ -28863,7 +28863,7 @@
         <v>37</v>
       </c>
       <c r="D123">
-        <v>0.30760000000000004</v>
+        <v>0.30759999999999998</v>
       </c>
       <c r="E123" t="s">
         <v>201</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D780FAC-8452-4D6A-970D-9C2E21B2D1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9F51603-04BE-413B-A16F-CCED9DF38B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -621,13 +621,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH04,S04aH03,S04aH02,S02aH03,S01aH02,S04aH04,S02aH02,S01aH03,S01aH05,S03aH03,S04aH05,S03aH05,S03aH04,S02aH04,S02aH05,S03aH02</t>
+    <t>S04aH03,S03aH04,S03aH02,S04aH05,S01aH04,S01aH03,S01aH02,S04aH04,S02aH03,S02aH02,S01aH05,S03aH05,S04aH02,S02aH04,S02aH05,S03aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH01,S01aH01,S04aH01,S04aH06,S03aH06,S03aH01,S01aH06,S02aH06</t>
+    <t>S02aH01,S03aH06,S01aH01,S04aH01,S04aH06,S03aH01,S02aH06,S01aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH01,S01aH01,S04aH01,S04aH06,S03aH06,S03aH01,S01aH06,S02aH06</v>
+        <v>S02aH01,S03aH06,S01aH01,S04aH01,S04aH06,S03aH01,S02aH06,S01aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH04,S04aH03,S04aH02,S02aH03,S01aH02,S04aH04,S02aH02,S01aH03,S01aH05,S03aH03,S04aH05,S03aH05,S03aH04,S02aH04,S02aH05,S03aH02</v>
+        <v>S04aH03,S03aH04,S03aH02,S04aH05,S01aH04,S01aH03,S01aH02,S04aH04,S02aH03,S02aH02,S01aH05,S03aH05,S04aH02,S02aH04,S02aH05,S03aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1350,7 +1350,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3711339-E622-4B1E-AC94-EB2EA417B073}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A86D96-701E-47D1-8EF2-9AE81F48476C}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1456,7 +1456,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E380A8F-AE41-4A9D-8CA6-C3C70652A7AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE1BB246-4D36-42F5-B817-EB4DAEACA3B5}">
   <dimension ref="B9:O490"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16878,7 +16878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A00FBD1-665D-4F6B-AE6F-9263BBFCBAB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F612314D-8E46-4B77-B0BC-B3910DE38F2C}">
   <dimension ref="B9:DH60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26051,7 +26051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{490BC121-4C6A-40EF-A6BD-288139276AE3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42673C1B-1994-42AF-ACF3-BFFCB132A02A}">
   <dimension ref="B9:E34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26417,7 +26417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDECE10C-6289-47E0-828D-B311FC98CC61}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D87D50AA-0FFD-45A1-9BE3-D5328CE7BC2D}">
   <dimension ref="B9:D58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26972,7 +26972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5774204-6DE7-4079-8CE8-10967C8294C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D0A2A2-993C-4972-B525-0A5339AEB796}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27263,7 +27263,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7769B53D-FFC0-4CA9-B08B-5E29887103AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96CE12D3-DC33-4C34-B4FF-571D03EB9D3F}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27407,7 +27407,7 @@
         <v>37</v>
       </c>
       <c r="D19">
-        <v>0.23839999999999997</v>
+        <v>0.23840000000000003</v>
       </c>
       <c r="E19" t="s">
         <v>201</v>
@@ -27421,7 +27421,7 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>0.23149999999999996</v>
+        <v>0.23150000000000001</v>
       </c>
       <c r="E20" t="s">
         <v>201</v>
@@ -27435,7 +27435,7 @@
         <v>43</v>
       </c>
       <c r="D21">
-        <v>0.12036666666666666</v>
+        <v>0.12036666666666668</v>
       </c>
       <c r="E21" t="s">
         <v>201</v>
@@ -27645,7 +27645,7 @@
         <v>41</v>
       </c>
       <c r="D36">
-        <v>0.32773333333333332</v>
+        <v>0.32773333333333338</v>
       </c>
       <c r="E36" t="s">
         <v>201</v>
@@ -27673,7 +27673,7 @@
         <v>45</v>
       </c>
       <c r="D38">
-        <v>0.20659999999999998</v>
+        <v>0.20660000000000001</v>
       </c>
       <c r="E38" t="s">
         <v>201</v>
@@ -27729,7 +27729,7 @@
         <v>45</v>
       </c>
       <c r="D42">
-        <v>0.29533333333333339</v>
+        <v>0.29533333333333334</v>
       </c>
       <c r="E42" t="s">
         <v>201</v>
@@ -27757,7 +27757,7 @@
         <v>41</v>
       </c>
       <c r="D44">
-        <v>0.34233333333333332</v>
+        <v>0.34233333333333338</v>
       </c>
       <c r="E44" t="s">
         <v>201</v>
@@ -27785,7 +27785,7 @@
         <v>45</v>
       </c>
       <c r="D46">
-        <v>0.22879999999999998</v>
+        <v>0.2288</v>
       </c>
       <c r="E46" t="s">
         <v>201</v>
@@ -27799,7 +27799,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="E47" t="s">
         <v>201</v>
@@ -27841,7 +27841,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.24779999999999999</v>
+        <v>0.24780000000000002</v>
       </c>
       <c r="E50" t="s">
         <v>201</v>
@@ -27855,7 +27855,7 @@
         <v>37</v>
       </c>
       <c r="D51">
-        <v>0.3167666666666667</v>
+        <v>0.31676666666666664</v>
       </c>
       <c r="E51" t="s">
         <v>201</v>
@@ -27897,7 +27897,7 @@
         <v>45</v>
       </c>
       <c r="D54">
-        <v>0.22766666666666668</v>
+        <v>0.22766666666666666</v>
       </c>
       <c r="E54" t="s">
         <v>201</v>
@@ -27925,7 +27925,7 @@
         <v>41</v>
       </c>
       <c r="D56">
-        <v>0.34999999999999992</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="E56" t="s">
         <v>201</v>
@@ -27967,7 +27967,7 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="E59" t="s">
         <v>201</v>
@@ -27995,7 +27995,7 @@
         <v>43</v>
       </c>
       <c r="D61">
-        <v>0.20516666666666664</v>
+        <v>0.20516666666666669</v>
       </c>
       <c r="E61" t="s">
         <v>201</v>
@@ -28037,7 +28037,7 @@
         <v>41</v>
       </c>
       <c r="D64">
-        <v>0.3297666666666666</v>
+        <v>0.32976666666666665</v>
       </c>
       <c r="E64" t="s">
         <v>201</v>
@@ -28065,7 +28065,7 @@
         <v>45</v>
       </c>
       <c r="D66">
-        <v>0.19193333333333332</v>
+        <v>0.19193333333333337</v>
       </c>
       <c r="E66" t="s">
         <v>201</v>
@@ -28079,7 +28079,7 @@
         <v>37</v>
       </c>
       <c r="D67">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="E67" t="s">
         <v>201</v>
@@ -28093,7 +28093,7 @@
         <v>41</v>
       </c>
       <c r="D68">
-        <v>0.38203333333333339</v>
+        <v>0.38203333333333328</v>
       </c>
       <c r="E68" t="s">
         <v>201</v>
@@ -28121,7 +28121,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.27233333333333337</v>
+        <v>0.27233333333333332</v>
       </c>
       <c r="E70" t="s">
         <v>201</v>
@@ -28163,7 +28163,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.19603333333333331</v>
+        <v>0.19603333333333336</v>
       </c>
       <c r="E73" t="s">
         <v>201</v>
@@ -28219,7 +28219,7 @@
         <v>43</v>
       </c>
       <c r="D77">
-        <v>0.21280000000000002</v>
+        <v>0.21279999999999999</v>
       </c>
       <c r="E77" t="s">
         <v>201</v>
@@ -28317,7 +28317,7 @@
         <v>41</v>
       </c>
       <c r="D84">
-        <v>0.33236666666666664</v>
+        <v>0.3323666666666667</v>
       </c>
       <c r="E84" t="s">
         <v>201</v>
@@ -28457,7 +28457,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.21929999999999997</v>
+        <v>0.21930000000000002</v>
       </c>
       <c r="E94" t="s">
         <v>201</v>
@@ -28583,7 +28583,7 @@
         <v>37</v>
       </c>
       <c r="D103">
-        <v>0.28609999999999997</v>
+        <v>0.28610000000000002</v>
       </c>
       <c r="E103" t="s">
         <v>201</v>
@@ -28597,7 +28597,7 @@
         <v>41</v>
       </c>
       <c r="D104">
-        <v>0.32653333333333334</v>
+        <v>0.32653333333333329</v>
       </c>
       <c r="E104" t="s">
         <v>201</v>
@@ -28611,7 +28611,7 @@
         <v>43</v>
       </c>
       <c r="D105">
-        <v>0.1952666666666667</v>
+        <v>0.19526666666666667</v>
       </c>
       <c r="E105" t="s">
         <v>201</v>
@@ -28625,7 +28625,7 @@
         <v>45</v>
       </c>
       <c r="D106">
-        <v>0.17756666666666665</v>
+        <v>0.17756666666666668</v>
       </c>
       <c r="E106" t="s">
         <v>201</v>
@@ -28639,7 +28639,7 @@
         <v>37</v>
       </c>
       <c r="D107">
-        <v>0.32646666666666668</v>
+        <v>0.32646666666666663</v>
       </c>
       <c r="E107" t="s">
         <v>201</v>
@@ -28765,7 +28765,7 @@
         <v>41</v>
       </c>
       <c r="D116">
-        <v>0.32293333333333329</v>
+        <v>0.32293333333333335</v>
       </c>
       <c r="E116" t="s">
         <v>201</v>
@@ -28807,7 +28807,7 @@
         <v>37</v>
       </c>
       <c r="D119">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="E119" t="s">
         <v>201</v>
@@ -28863,7 +28863,7 @@
         <v>37</v>
       </c>
       <c r="D123">
-        <v>0.30759999999999998</v>
+        <v>0.30760000000000004</v>
       </c>
       <c r="E123" t="s">
         <v>201</v>
@@ -28877,7 +28877,7 @@
         <v>41</v>
       </c>
       <c r="D124">
-        <v>0.3557333333333334</v>
+        <v>0.35573333333333329</v>
       </c>
       <c r="E124" t="s">
         <v>201</v>
@@ -28891,7 +28891,7 @@
         <v>43</v>
       </c>
       <c r="D125">
-        <v>0.17353333333333332</v>
+        <v>0.17353333333333334</v>
       </c>
       <c r="E125" t="s">
         <v>201</v>
@@ -28905,7 +28905,7 @@
         <v>45</v>
       </c>
       <c r="D126">
-        <v>0.21530000000000002</v>
+        <v>0.21529999999999996</v>
       </c>
       <c r="E126" t="s">
         <v>201</v>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9F51603-04BE-413B-A16F-CCED9DF38B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{594635DD-0858-4083-9494-91A53D8C8628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -621,13 +621,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH03,S03aH04,S03aH02,S04aH05,S01aH04,S01aH03,S01aH02,S04aH04,S02aH03,S02aH02,S01aH05,S03aH05,S04aH02,S02aH04,S02aH05,S03aH03</t>
+    <t>S01aH04,S04aH03,S03aH04,S02aH04,S02aH05,S04aH02,S03aH05,S04aH05,S03aH03,S02aH02,S01aH02,S04aH04,S02aH03,S03aH02,S01aH03,S01aH05</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH01,S03aH06,S01aH01,S04aH01,S04aH06,S03aH01,S02aH06,S01aH06</t>
+    <t>S02aH01,S01aH06,S02aH06,S03aH01,S03aH06,S01aH01,S04aH01,S04aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH01,S03aH06,S01aH01,S04aH01,S04aH06,S03aH01,S02aH06,S01aH06</v>
+        <v>S02aH01,S01aH06,S02aH06,S03aH01,S03aH06,S01aH01,S04aH01,S04aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S04aH03,S03aH04,S03aH02,S04aH05,S01aH04,S01aH03,S01aH02,S04aH04,S02aH03,S02aH02,S01aH05,S03aH05,S04aH02,S02aH04,S02aH05,S03aH03</v>
+        <v>S01aH04,S04aH03,S03aH04,S02aH04,S02aH05,S04aH02,S03aH05,S04aH05,S03aH03,S02aH02,S01aH02,S04aH04,S02aH03,S03aH02,S01aH03,S01aH05</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1350,7 +1350,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A86D96-701E-47D1-8EF2-9AE81F48476C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC22E39-D0E2-4B8B-8693-53E55A3EC341}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1456,7 +1456,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE1BB246-4D36-42F5-B817-EB4DAEACA3B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80723231-EF9C-460D-97E9-E0C643956C32}">
   <dimension ref="B9:O490"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16878,7 +16878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F612314D-8E46-4B77-B0BC-B3910DE38F2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72C43F6A-E8C8-4865-B0CD-AC1B9BF9A296}">
   <dimension ref="B9:DH60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26051,7 +26051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42673C1B-1994-42AF-ACF3-BFFCB132A02A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA67D83C-80CC-4454-83C5-27D71898CCF1}">
   <dimension ref="B9:E34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26417,7 +26417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D87D50AA-0FFD-45A1-9BE3-D5328CE7BC2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{052A48EE-7DFD-4EFC-8530-9EA60F8E68BB}">
   <dimension ref="B9:D58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26972,7 +26972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D0A2A2-993C-4972-B525-0A5339AEB796}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F92FBE37-B37B-4045-BF5C-13AAFEBEF86E}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27263,7 +27263,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96CE12D3-DC33-4C34-B4FF-571D03EB9D3F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{356AA730-5EFA-4B73-8E59-FE7426D0A82B}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27309,7 +27309,7 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>0.17526666666666668</v>
+        <v>0.17526666666666665</v>
       </c>
       <c r="E12" t="s">
         <v>201</v>
@@ -27491,7 +27491,7 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>0.24466666666666667</v>
+        <v>0.2446666666666667</v>
       </c>
       <c r="E25" t="s">
         <v>201</v>
@@ -27869,7 +27869,7 @@
         <v>41</v>
       </c>
       <c r="D52">
-        <v>0.3227666666666667</v>
+        <v>0.32276666666666665</v>
       </c>
       <c r="E52" t="s">
         <v>201</v>
@@ -27939,7 +27939,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.18733333333333332</v>
+        <v>0.18733333333333335</v>
       </c>
       <c r="E57" t="s">
         <v>201</v>
@@ -27995,7 +27995,7 @@
         <v>43</v>
       </c>
       <c r="D61">
-        <v>0.20516666666666669</v>
+        <v>0.20516666666666664</v>
       </c>
       <c r="E61" t="s">
         <v>201</v>
@@ -28037,7 +28037,7 @@
         <v>41</v>
       </c>
       <c r="D64">
-        <v>0.32976666666666665</v>
+        <v>0.3297666666666666</v>
       </c>
       <c r="E64" t="s">
         <v>201</v>
@@ -28051,7 +28051,7 @@
         <v>43</v>
       </c>
       <c r="D65">
-        <v>0.20076666666666668</v>
+        <v>0.20076666666666665</v>
       </c>
       <c r="E65" t="s">
         <v>201</v>
@@ -28163,7 +28163,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.19603333333333336</v>
+        <v>0.19603333333333331</v>
       </c>
       <c r="E73" t="s">
         <v>201</v>
@@ -28219,7 +28219,7 @@
         <v>43</v>
       </c>
       <c r="D77">
-        <v>0.21279999999999999</v>
+        <v>0.21280000000000002</v>
       </c>
       <c r="E77" t="s">
         <v>201</v>
@@ -28429,7 +28429,7 @@
         <v>41</v>
       </c>
       <c r="D92">
-        <v>0.31546666666666673</v>
+        <v>0.31546666666666667</v>
       </c>
       <c r="E92" t="s">
         <v>201</v>
@@ -28653,7 +28653,7 @@
         <v>41</v>
       </c>
       <c r="D108">
-        <v>0.32569999999999993</v>
+        <v>0.32569999999999999</v>
       </c>
       <c r="E108" t="s">
         <v>201</v>
@@ -28877,7 +28877,7 @@
         <v>41</v>
       </c>
       <c r="D124">
-        <v>0.35573333333333329</v>
+        <v>0.3557333333333334</v>
       </c>
       <c r="E124" t="s">
         <v>201</v>
@@ -28891,7 +28891,7 @@
         <v>43</v>
       </c>
       <c r="D125">
-        <v>0.17353333333333334</v>
+        <v>0.17353333333333332</v>
       </c>
       <c r="E125" t="s">
         <v>201</v>
